--- a/testing.xlsx
+++ b/testing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ca033a4b21f120b5/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Dropbox\Streamlit\Test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="8_{ABDABC44-9B11-43FC-97EA-28BF0B0D88B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAA5BA9B-5B77-482A-97AE-BA8459F2FFB7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F326417-EB90-4E93-B9B3-30999F3494D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{F3C6EDD6-2500-4912-B412-741BE536D06C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Act</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Dec</t>
+  </si>
+  <si>
+    <t>PPY</t>
   </si>
 </sst>
 </file>
@@ -145,10 +148,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -468,10 +467,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F81B0FF3-8195-499C-94FC-A8A13ABED2B6}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -484,8 +483,11 @@
       <c r="D1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -498,8 +500,11 @@
       <c r="D2">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -512,8 +517,11 @@
       <c r="D3">
         <v>118</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -526,8 +534,11 @@
       <c r="D4">
         <v>122</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E4">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -540,8 +551,11 @@
       <c r="D5">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -554,8 +568,11 @@
       <c r="D6">
         <v>112</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E6">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -568,8 +585,11 @@
       <c r="D7">
         <v>112</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E7">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -582,8 +602,11 @@
       <c r="D8">
         <v>107</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E8">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -596,8 +619,11 @@
       <c r="D9">
         <v>119</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E9">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -610,8 +636,11 @@
       <c r="D10">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E10">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -624,8 +653,11 @@
       <c r="D11">
         <v>101</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -638,8 +670,11 @@
       <c r="D12">
         <v>121</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -651,6 +686,9 @@
       </c>
       <c r="D13">
         <v>100</v>
+      </c>
+      <c r="E13">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
